--- a/excel/Weekends_2027年度_目標と報奨金_店長説明用.xlsx
+++ b/excel/Weekends_2027年度_目標と報奨金_店長説明用.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yataka-02\AppData\Local\Temp\claude\C--Users-yataka-02-Desktop-Claude\76fa42a7-01fc-42d8-86c7-11cf90447c56\scratchpad\margin-calculator\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1717098-5285-4A60-A85B-C05CACFAA99C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44929888-FD82-4D28-9B4F-64E82DFF090F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="目標と報奨金" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
     <t>前年の売上（参考）</t>
   </si>
   <si>
-    <t>月ごとの目標は、店長さんがスマレジに登録した予算（年6,000万円）の月ごとの比率をもとに決めました。売上は10万円単位、粗利は5万円単位にそろえています。</t>
+    <t>月ごとの目標は、店長さんがスマレジに登録した予算（年6,000万円）の月ごとの比率をもとに決めました。売上の少ない月（8・9・2・4・5・7月）も、お店の経費をまかなえるよう粗利180万円・売上530万円にしています。</t>
   </si>
   <si>
     <t>2. 月ごとの目標</t>
@@ -788,17 +788,17 @@
     <row r="6" spans="1:8" ht="30" customHeight="1">
       <c r="A6" s="17">
         <f>E23</f>
-        <v>6300</v>
+        <v>6860</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="17">
         <f>F23</f>
-        <v>2150</v>
+        <v>2340</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="28">
         <f>C6/A6</f>
-        <v>0.34126984126984128</v>
+        <v>0.34110787172011664</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="17">
@@ -864,18 +864,18 @@
         <v>304</v>
       </c>
       <c r="E11" s="5">
-        <v>370</v>
+        <v>530</v>
       </c>
       <c r="F11" s="6">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ref="G11:G22" si="0">ROUND(F11*1.05/5,0)*5</f>
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H11" s="7">
         <f t="shared" ref="H11:H23" si="1">F11/B11</f>
-        <v>4.6296296296296298</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15">
@@ -892,18 +892,18 @@
         <v>364</v>
       </c>
       <c r="E12" s="5">
-        <v>470</v>
+        <v>530</v>
       </c>
       <c r="F12" s="6">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="0"/>
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="H12" s="7">
         <f t="shared" si="1"/>
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15">
@@ -1032,18 +1032,18 @@
         <v>280</v>
       </c>
       <c r="E17" s="5">
-        <v>370</v>
+        <v>530</v>
       </c>
       <c r="F17" s="6">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="0"/>
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H17" s="7">
         <f t="shared" si="1"/>
-        <v>5.208333333333333</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15">
@@ -1088,18 +1088,18 @@
         <v>358</v>
       </c>
       <c r="E19" s="5">
-        <v>470</v>
+        <v>530</v>
       </c>
       <c r="F19" s="6">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="0"/>
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="H19" s="7">
         <f t="shared" si="1"/>
-        <v>6.1538461538461542</v>
+        <v>6.9230769230769234</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15">
@@ -1116,18 +1116,18 @@
         <v>480</v>
       </c>
       <c r="E20" s="5">
-        <v>470</v>
+        <v>530</v>
       </c>
       <c r="F20" s="6">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="0"/>
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="H20" s="7">
         <f t="shared" si="1"/>
-        <v>5.9259259259259256</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15">
@@ -1172,18 +1172,18 @@
         <v>474</v>
       </c>
       <c r="E22" s="5">
-        <v>470</v>
+        <v>530</v>
       </c>
       <c r="F22" s="6">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="0"/>
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="H22" s="7">
         <f t="shared" si="1"/>
-        <v>5.9259259259259256</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15">
@@ -1204,19 +1204,19 @@
       </c>
       <c r="E23" s="10">
         <f t="shared" si="2"/>
-        <v>6300</v>
+        <v>6860</v>
       </c>
       <c r="F23" s="10">
         <f t="shared" si="2"/>
-        <v>2150</v>
+        <v>2340</v>
       </c>
       <c r="G23" s="10">
         <f t="shared" si="2"/>
-        <v>2265</v>
+        <v>2465</v>
       </c>
       <c r="H23" s="11">
         <f t="shared" si="1"/>
-        <v>6.8690095846645365</v>
+        <v>7.4760383386581468</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="36" customHeight="1">

--- a/excel/Weekends_2027年度_目標と報奨金_店長説明用.xlsx
+++ b/excel/Weekends_2027年度_目標と報奨金_店長説明用.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yataka-02\AppData\Local\Temp\claude\C--Users-yataka-02-Desktop-Claude\76fa42a7-01fc-42d8-86c7-11cf90447c56\scratchpad\margin-calculator\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44929888-FD82-4D28-9B4F-64E82DFF090F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850BBF8C-21DD-4CCB-8B54-7F324A6C4B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
     <t>前年の売上（参考）</t>
   </si>
   <si>
-    <t>月ごとの目標は、店長さんがスマレジに登録した予算（年6,000万円）の月ごとの比率をもとに決めました。売上の少ない月（8・9・2・4・5・7月）も、お店の経費をまかなえるよう粗利180万円・売上530万円にしています。</t>
+    <t>月ごとの目標は、前年の売上をもとに、どの月も無理のない伸び（前年の1.1〜1.4倍）にそろえて決めました。売上の少ない月（8・9・2・4月）は少し高めにして、お店の経費をまかなえる水準に近づけています。</t>
   </si>
   <si>
     <t>2. 月ごとの目標</t>
@@ -158,7 +158,7 @@
     <t>お店全体（月）</t>
   </si>
   <si>
-    <t>例）粗利の目標が200万円の月（10月）の場合</t>
+    <t>例）粗利の目標が190万円の月（11月）の場合</t>
   </si>
   <si>
     <t>その月の粗利</t>
@@ -173,10 +173,10 @@
     <t>達成ラインに届かず</t>
   </si>
   <si>
-    <t>達成ライン（200万円）以上</t>
-  </si>
-  <si>
-    <t>105%ライン（210万円）以上</t>
+    <t>達成ライン（190万円）以上</t>
+  </si>
+  <si>
+    <t>105%ライン（200万円）以上</t>
   </si>
   <si>
     <t>4. 大事なルール</t>
@@ -788,17 +788,17 @@
     <row r="6" spans="1:8" ht="30" customHeight="1">
       <c r="A6" s="17">
         <f>E23</f>
-        <v>6860</v>
+        <v>6300</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="17">
         <f>F23</f>
-        <v>2340</v>
+        <v>2150</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="28">
         <f>C6/A6</f>
-        <v>0.34110787172011664</v>
+        <v>0.34126984126984128</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="17">
@@ -864,18 +864,18 @@
         <v>304</v>
       </c>
       <c r="E11" s="5">
-        <v>530</v>
+        <v>420</v>
       </c>
       <c r="F11" s="6">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ref="G11:G22" si="0">ROUND(F11*1.05/5,0)*5</f>
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="H11" s="7">
         <f t="shared" ref="H11:H23" si="1">F11/B11</f>
-        <v>6.666666666666667</v>
+        <v>5.3703703703703702</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15">
@@ -892,18 +892,18 @@
         <v>364</v>
       </c>
       <c r="E12" s="5">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="F12" s="6">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="0"/>
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="H12" s="7">
         <f t="shared" si="1"/>
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15">
@@ -920,18 +920,18 @@
         <v>493</v>
       </c>
       <c r="E13" s="5">
-        <v>580</v>
+        <v>540</v>
       </c>
       <c r="F13" s="6">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="0"/>
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="H13" s="7">
         <f t="shared" si="1"/>
-        <v>7.4074074074074074</v>
+        <v>6.8518518518518521</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15">
@@ -948,18 +948,18 @@
         <v>515</v>
       </c>
       <c r="E14" s="5">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="F14" s="6">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="0"/>
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H14" s="7">
         <f t="shared" si="1"/>
-        <v>7.6923076923076925</v>
+        <v>7.3076923076923075</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15">
@@ -976,18 +976,18 @@
         <v>682</v>
       </c>
       <c r="E15" s="5">
-        <v>730</v>
+        <v>750</v>
       </c>
       <c r="F15" s="6">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="0"/>
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="H15" s="7">
         <f t="shared" si="1"/>
-        <v>9.615384615384615</v>
+        <v>9.8076923076923084</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15">
@@ -1004,18 +1004,18 @@
         <v>485</v>
       </c>
       <c r="E16" s="5">
-        <v>630</v>
+        <v>530</v>
       </c>
       <c r="F16" s="6">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="0"/>
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="H16" s="7">
         <f t="shared" si="1"/>
-        <v>7.7777777777777777</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15">
@@ -1032,18 +1032,18 @@
         <v>280</v>
       </c>
       <c r="E17" s="5">
-        <v>530</v>
+        <v>390</v>
       </c>
       <c r="F17" s="6">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="0"/>
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="H17" s="7">
         <f t="shared" si="1"/>
-        <v>7.5</v>
+        <v>5.625</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15">
@@ -1060,18 +1060,18 @@
         <v>442</v>
       </c>
       <c r="E18" s="5">
-        <v>580</v>
+        <v>530</v>
       </c>
       <c r="F18" s="6">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="0"/>
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="H18" s="7">
         <f t="shared" si="1"/>
-        <v>7.6923076923076925</v>
+        <v>6.9230769230769234</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15">
@@ -1088,18 +1088,18 @@
         <v>358</v>
       </c>
       <c r="E19" s="5">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="F19" s="6">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="0"/>
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="H19" s="7">
         <f t="shared" si="1"/>
-        <v>6.9230769230769234</v>
+        <v>6.5384615384615383</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15">
@@ -1144,18 +1144,18 @@
         <v>489</v>
       </c>
       <c r="E21" s="5">
-        <v>580</v>
+        <v>530</v>
       </c>
       <c r="F21" s="6">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="0"/>
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="H21" s="7">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15">
@@ -1172,7 +1172,7 @@
         <v>474</v>
       </c>
       <c r="E22" s="5">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="F22" s="6">
         <v>180</v>
@@ -1204,19 +1204,19 @@
       </c>
       <c r="E23" s="10">
         <f t="shared" si="2"/>
-        <v>6860</v>
+        <v>6300</v>
       </c>
       <c r="F23" s="10">
         <f t="shared" si="2"/>
-        <v>2340</v>
+        <v>2150</v>
       </c>
       <c r="G23" s="10">
         <f t="shared" si="2"/>
-        <v>2465</v>
+        <v>2265</v>
       </c>
       <c r="H23" s="11">
         <f t="shared" si="1"/>
-        <v>7.4760383386581468</v>
+        <v>6.8690095846645365</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="36" customHeight="1">
@@ -1339,7 +1339,7 @@
     </row>
     <row r="35" spans="1:8" ht="15">
       <c r="A35" s="22">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="24" t="s">
@@ -1356,7 +1356,7 @@
     </row>
     <row r="36" spans="1:8" ht="15">
       <c r="A36" s="22">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="24" t="s">
@@ -1373,7 +1373,7 @@
     </row>
     <row r="37" spans="1:8" ht="15">
       <c r="A37" s="22">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="24" t="s">

--- a/excel/Weekends_2027年度_目標と報奨金_店長説明用.xlsx
+++ b/excel/Weekends_2027年度_目標と報奨金_店長説明用.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yataka-02\AppData\Local\Temp\claude\C--Users-yataka-02-Desktop-Claude\76fa42a7-01fc-42d8-86c7-11cf90447c56\scratchpad\margin-calculator\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850BBF8C-21DD-4CCB-8B54-7F324A6C4B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCDC5CD-54FD-4DA2-81A6-2A0665C68AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
     <t>毎月の「粗利」の目標を達成したら、お店のみんなに報奨金を出します。金額はすべて税抜です。</t>
   </si>
   <si>
-    <t>1. 1年間の目標</t>
+    <t>1. 1年間の目標（月ごとの目標の合計）</t>
   </si>
   <si>
     <t>売上の目標</t>
@@ -59,7 +59,7 @@
     <t>前年の売上（参考）</t>
   </si>
   <si>
-    <t>月ごとの目標は、前年の売上をもとに、どの月も無理のない伸び（前年の1.1〜1.4倍）にそろえて決めました。売上の少ない月（8・9・2・4月）は少し高めにして、お店の経費をまかなえる水準に近づけています。</t>
+    <t>月ごとの目標は、店長さんがスマレジに登録した予算をもとに決めました（売上は予算どおり、粗利は予算×粗利率）。売上の少ない月（8・9・2・4・5・7月）は、お店の経費をまかなえる粗利180万円・売上530万円にしています。</t>
   </si>
   <si>
     <t>2. 月ごとの目標</t>
@@ -788,17 +788,17 @@
     <row r="6" spans="1:8" ht="30" customHeight="1">
       <c r="A6" s="17">
         <f>E23</f>
-        <v>6300</v>
+        <v>6680</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="17">
         <f>F23</f>
-        <v>2150</v>
+        <v>2285</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="28">
         <f>C6/A6</f>
-        <v>0.34126984126984128</v>
+        <v>0.34206586826347307</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="17">
@@ -864,18 +864,18 @@
         <v>304</v>
       </c>
       <c r="E11" s="5">
-        <v>420</v>
+        <v>530</v>
       </c>
       <c r="F11" s="6">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ref="G11:G22" si="0">ROUND(F11*1.05/5,0)*5</f>
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="H11" s="7">
         <f t="shared" ref="H11:H23" si="1">F11/B11</f>
-        <v>5.3703703703703702</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15">
@@ -892,18 +892,18 @@
         <v>364</v>
       </c>
       <c r="E12" s="5">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="F12" s="6">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="0"/>
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="H12" s="7">
         <f t="shared" si="1"/>
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15">
@@ -920,18 +920,18 @@
         <v>493</v>
       </c>
       <c r="E13" s="5">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="F13" s="6">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="0"/>
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H13" s="7">
         <f t="shared" si="1"/>
-        <v>6.8518518518518521</v>
+        <v>7.0370370370370372</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15">
@@ -948,7 +948,7 @@
         <v>515</v>
       </c>
       <c r="E14" s="5">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="F14" s="6">
         <v>190</v>
@@ -976,18 +976,18 @@
         <v>682</v>
       </c>
       <c r="E15" s="5">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="F15" s="6">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="0"/>
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="H15" s="7">
         <f t="shared" si="1"/>
-        <v>9.8076923076923084</v>
+        <v>9.2307692307692299</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15">
@@ -1004,18 +1004,18 @@
         <v>485</v>
       </c>
       <c r="E16" s="5">
-        <v>530</v>
+        <v>600</v>
       </c>
       <c r="F16" s="6">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="0"/>
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="H16" s="7">
         <f t="shared" si="1"/>
-        <v>6.666666666666667</v>
+        <v>7.5925925925925926</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15">
@@ -1032,18 +1032,18 @@
         <v>280</v>
       </c>
       <c r="E17" s="5">
-        <v>390</v>
+        <v>530</v>
       </c>
       <c r="F17" s="6">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="0"/>
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="H17" s="7">
         <f t="shared" si="1"/>
-        <v>5.625</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15">
@@ -1060,18 +1060,18 @@
         <v>442</v>
       </c>
       <c r="E18" s="5">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="F18" s="6">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="0"/>
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="H18" s="7">
         <f t="shared" si="1"/>
-        <v>6.9230769230769234</v>
+        <v>7.3076923076923075</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15">
@@ -1088,18 +1088,18 @@
         <v>358</v>
       </c>
       <c r="E19" s="5">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="F19" s="6">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="0"/>
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="H19" s="7">
         <f t="shared" si="1"/>
-        <v>6.5384615384615383</v>
+        <v>6.9230769230769234</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15">
@@ -1144,18 +1144,18 @@
         <v>489</v>
       </c>
       <c r="E21" s="5">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="F21" s="6">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="0"/>
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="H21" s="7">
         <f t="shared" si="1"/>
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15">
@@ -1172,7 +1172,7 @@
         <v>474</v>
       </c>
       <c r="E22" s="5">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="F22" s="6">
         <v>180</v>
@@ -1204,19 +1204,19 @@
       </c>
       <c r="E23" s="10">
         <f t="shared" si="2"/>
-        <v>6300</v>
+        <v>6680</v>
       </c>
       <c r="F23" s="10">
         <f t="shared" si="2"/>
-        <v>2150</v>
+        <v>2285</v>
       </c>
       <c r="G23" s="10">
         <f t="shared" si="2"/>
-        <v>2265</v>
+        <v>2405</v>
       </c>
       <c r="H23" s="11">
         <f t="shared" si="1"/>
-        <v>6.8690095846645365</v>
+        <v>7.3003194888178911</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="36" customHeight="1">
